--- a/data/trans_orig/P23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200615</t>
+          <t>200966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>244785</t>
+          <t>246032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158785</t>
+          <t>159092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191854</t>
+          <t>194484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>370586</t>
+          <t>372438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427328</t>
+          <t>429929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80129</t>
+          <t>81590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118756</t>
+          <t>117623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115840</t>
+          <t>115709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158078</t>
+          <t>158370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118212</t>
+          <t>119801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158683</t>
+          <t>157760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66982</t>
+          <t>66785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98135</t>
+          <t>98554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195760</t>
+          <t>195609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246589</t>
+          <t>245757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132101</t>
+          <t>131667</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169623</t>
+          <t>170129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177660</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215470</t>
+          <t>215606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>316777</t>
+          <t>321913</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>373002</t>
+          <t>377470</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>65035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100061</t>
+          <t>96865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31209</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102315</t>
+          <t>103308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144779</t>
+          <t>143793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109869</t>
+          <t>110312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147737</t>
+          <t>147278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99423</t>
+          <t>99353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134988</t>
+          <t>137325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>219347</t>
+          <t>216431</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>272721</t>
+          <t>271096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156998</t>
+          <t>158330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203118</t>
+          <t>204783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84820</t>
+          <t>84446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109723</t>
+          <t>109766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254457</t>
+          <t>249994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303695</t>
+          <t>301296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>90036</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>128052</t>
+          <t>127016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>33993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152167</t>
+          <t>154047</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>218377</t>
+          <t>219637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267174</t>
+          <t>263805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54339</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259818</t>
+          <t>260926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>312366</t>
+          <t>311245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>368994</t>
+          <t>366817</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>436984</t>
+          <t>434101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>382985</t>
+          <t>383331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>434291</t>
+          <t>435211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>763894</t>
+          <t>766692</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>850594</t>
+          <t>854846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246121</t>
+          <t>244651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303154</t>
+          <t>301863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>50362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80053</t>
+          <t>81573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304780</t>
+          <t>306008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369861</t>
+          <t>371766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>28794</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36706</t>
+          <t>36887</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64913</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>498633</t>
+          <t>500530</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>568565</t>
+          <t>569820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198648</t>
+          <t>198059</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>247323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>711982</t>
+          <t>711167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>796179</t>
+          <t>799186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82255</t>
+          <t>82448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118013</t>
+          <t>116504</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>326036</t>
+          <t>323938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>371787</t>
+          <t>372970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>416424</t>
+          <t>412694</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>476419</t>
+          <t>479897</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51624</t>
+          <t>51202</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51035</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85717</t>
+          <t>86961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123266</t>
+          <t>125162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>162632</t>
+          <t>163805</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>199952</t>
+          <t>201332</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>144476</t>
+          <t>144133</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>188427</t>
+          <t>188354</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>319066</t>
+          <t>315824</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>378044</t>
+          <t>380427</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>186886</t>
+          <t>188605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>218470</t>
+          <t>219076</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1003497</t>
+          <t>1001316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1055271</t>
+          <t>1055397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1203808</t>
+          <t>1200075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1263609</t>
+          <t>1262254</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64449</t>
+          <t>62776</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>40688</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70531</t>
+          <t>69973</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49011</t>
+          <t>49598</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86744</t>
+          <t>87063</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>127383</t>
+          <t>129832</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>173195</t>
+          <t>173888</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>195327</t>
+          <t>196717</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>248153</t>
+          <t>250214</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1198885</t>
+          <t>1202151</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1309872</t>
+          <t>1314257</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2203966</t>
+          <t>2203643</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2310348</t>
+          <t>2313629</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3433355</t>
+          <t>3432978</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3595262</t>
+          <t>3602558</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>587289</t>
+          <t>582596</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>680898</t>
+          <t>674154</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>227806</t>
+          <t>227695</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>289226</t>
+          <t>288229</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>830195</t>
+          <t>833659</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>939028</t>
+          <t>951343</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69021</t>
+          <t>67363</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>105479</t>
+          <t>103795</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>68099</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>102400</t>
+          <t>105600</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>147998</t>
+          <t>145386</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>197852</t>
+          <t>196421</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1242529</t>
+          <t>1240952</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1359056</t>
+          <t>1354630</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>733785</t>
+          <t>726506</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>830558</t>
+          <t>821358</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2002508</t>
+          <t>2002032</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2155963</t>
+          <t>2155898</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155320</t>
+          <t>154923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198450</t>
+          <t>198086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143552</t>
+          <t>143378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179802</t>
+          <t>179108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308582</t>
+          <t>311951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>367857</t>
+          <t>369585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94139</t>
+          <t>94352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132472</t>
+          <t>133980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40017</t>
+          <t>39702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>68495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140094</t>
+          <t>142476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191201</t>
+          <t>191180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117856</t>
+          <t>119809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159249</t>
+          <t>162288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73809</t>
+          <t>72818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>107333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202675</t>
+          <t>202691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256459</t>
+          <t>256633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>151889</t>
+          <t>154237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>196125</t>
+          <t>198214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137706</t>
+          <t>138637</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177349</t>
+          <t>177145</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>305892</t>
+          <t>306211</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>362386</t>
+          <t>363155</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76288</t>
+          <t>75480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111691</t>
+          <t>111744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41425</t>
+          <t>40683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68951</t>
+          <t>69117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125281</t>
+          <t>124186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172546</t>
+          <t>170893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35952</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>119145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161504</t>
+          <t>158126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97236</t>
+          <t>97057</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134356</t>
+          <t>133164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225448</t>
+          <t>226664</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165070</t>
+          <t>163303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213393</t>
+          <t>213953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121859</t>
+          <t>123827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155633</t>
+          <t>156221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>298720</t>
+          <t>297106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358013</t>
+          <t>357282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146808</t>
+          <t>145782</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>193655</t>
+          <t>190495</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48294</t>
+          <t>48957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178079</t>
+          <t>176222</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>227882</t>
+          <t>234704</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27192</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233083</t>
+          <t>233727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282840</t>
+          <t>285974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64563</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95480</t>
+          <t>93297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>305779</t>
+          <t>306356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364419</t>
+          <t>366979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>296583</t>
+          <t>297133</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>362962</t>
+          <t>360230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>336223</t>
+          <t>337274</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394008</t>
+          <t>394972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>650765</t>
+          <t>650203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>736488</t>
+          <t>738340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297984</t>
+          <t>300537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362109</t>
+          <t>361610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94771</t>
+          <t>94956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133792</t>
+          <t>135730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>404237</t>
+          <t>405378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485077</t>
+          <t>481597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>40503</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29501</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32137</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60639</t>
+          <t>61452</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>438460</t>
+          <t>435598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>506822</t>
+          <t>506014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>240367</t>
+          <t>240548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295169</t>
+          <t>294667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>693733</t>
+          <t>696654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>783245</t>
+          <t>785755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141810</t>
+          <t>138097</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>183006</t>
+          <t>182909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>444206</t>
+          <t>446606</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>499702</t>
+          <t>498777</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>597452</t>
+          <t>600590</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>672255</t>
+          <t>672559</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112028</t>
+          <t>111400</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>151527</t>
+          <t>151801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>56551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88078</t>
+          <t>91686</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>177101</t>
+          <t>174906</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231061</t>
+          <t>228818</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>41402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>182349</t>
+          <t>180572</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>226054</t>
+          <t>225996</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>176776</t>
+          <t>177357</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>228810</t>
+          <t>225724</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>370629</t>
+          <t>371815</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>436747</t>
+          <t>441295</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>182200</t>
+          <t>180261</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>211110</t>
+          <t>210709</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>854926</t>
+          <t>853332</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>906829</t>
+          <t>908466</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1047598</t>
+          <t>1049192</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1107992</t>
+          <t>1110949</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7907,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48142</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79565</t>
+          <t>81184</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54258</t>
+          <t>53591</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>87996</t>
+          <t>88745</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>43052</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59438</t>
+          <t>58816</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>128771</t>
+          <t>129983</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>174907</t>
+          <t>175235</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>172209</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>224281</t>
+          <t>224720</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1167503</t>
+          <t>1171255</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1286373</t>
+          <t>1290709</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2119405</t>
+          <t>2124880</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2240384</t>
+          <t>2242604</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3319656</t>
+          <t>3323450</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3490783</t>
+          <t>3491352</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>782428</t>
+          <t>786718</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>892427</t>
+          <t>886402</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>351653</t>
+          <t>350579</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>430987</t>
+          <t>431751</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1161265</t>
+          <t>1166612</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1295697</t>
+          <t>1299018</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>75968</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>116140</t>
+          <t>120744</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>57358</t>
+          <t>55682</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>92450</t>
+          <t>92681</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>142879</t>
+          <t>145380</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>200970</t>
+          <t>198099</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1201528</t>
+          <t>1195626</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1321281</t>
+          <t>1314748</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>848074</t>
+          <t>843704</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>961081</t>
+          <t>954558</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2079118</t>
+          <t>2087589</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2245221</t>
+          <t>2252006</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197182</t>
+          <t>197925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239896</t>
+          <t>240560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191986</t>
+          <t>192110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228385</t>
+          <t>230363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>401619</t>
+          <t>399685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>461558</t>
+          <t>457864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84397</t>
+          <t>84145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>119874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54320</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85729</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148945</t>
+          <t>148848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196108</t>
+          <t>193234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112508</t>
+          <t>112135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75387</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>129126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178317</t>
+          <t>175598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164757</t>
+          <t>166641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>206072</t>
+          <t>206165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180137</t>
+          <t>181999</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220278</t>
+          <t>220586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>357142</t>
+          <t>360795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>414729</t>
+          <t>417539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68540</t>
+          <t>68551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100563</t>
+          <t>100897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133337</t>
+          <t>131516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178460</t>
+          <t>177720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,82 +9976,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7738</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14482</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>19377</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>11870</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>30765</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7738</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3801</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>15281</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>4,12%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>19377</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>11715</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>30880</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77919</t>
+          <t>78210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111737</t>
+          <t>112192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76686</t>
+          <t>75456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110462</t>
+          <t>111041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>212608</t>
+          <t>211302</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163275</t>
+          <t>165967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210218</t>
+          <t>210640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>83877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109885</t>
+          <t>109568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260172</t>
+          <t>260234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310300</t>
+          <t>312401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>99205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135791</t>
+          <t>137937</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115862</t>
+          <t>114496</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>157178</t>
+          <t>157274</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178636</t>
+          <t>179793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225394</t>
+          <t>225020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58691</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223783</t>
+          <t>224165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274118</t>
+          <t>276612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>415191</t>
+          <t>414289</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>481144</t>
+          <t>482575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>380376</t>
+          <t>378473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>435653</t>
+          <t>438656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>813905</t>
+          <t>813961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>900407</t>
+          <t>905908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234556</t>
+          <t>232900</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293854</t>
+          <t>290960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83016</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121607</t>
+          <t>122678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325302</t>
+          <t>326542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>393697</t>
+          <t>394548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45808</t>
+          <t>45202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48758</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>80892</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>370818</t>
+          <t>371853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>436796</t>
+          <t>441491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>258879</t>
+          <t>259096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310451</t>
+          <t>313286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>650571</t>
+          <t>644590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>731614</t>
+          <t>729266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>223768</t>
+          <t>225228</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>273284</t>
+          <t>275194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408984</t>
+          <t>409795</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>463533</t>
+          <t>465477</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>649838</t>
+          <t>651861</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>722172</t>
+          <t>727648</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>107892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149343</t>
+          <t>149645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67043</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>101886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184210</t>
+          <t>185429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237033</t>
+          <t>240435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,47 +11718,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>17712</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>28067</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>17712</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>10918</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>28326</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>210476</t>
+          <t>207395</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>257695</t>
+          <t>258786</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>185583</t>
+          <t>184909</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234380</t>
+          <t>235477</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>408938</t>
+          <t>407935</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>478274</t>
+          <t>476963</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>192575</t>
+          <t>190827</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>221598</t>
+          <t>222232</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>831203</t>
+          <t>827937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>884270</t>
+          <t>885983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1036289</t>
+          <t>1036297</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1098427</t>
+          <t>1097698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62133</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>68023</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>51377</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>79839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>138421</t>
+          <t>135873</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>185225</t>
+          <t>187271</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>198250</t>
+          <t>197126</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>251575</t>
+          <t>253547</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1443703</t>
+          <t>1435251</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1558145</t>
+          <t>1553266</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2154959</t>
+          <t>2158313</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2272918</t>
+          <t>2274102</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3630587</t>
+          <t>3629976</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3797021</t>
+          <t>3807182</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>651797</t>
+          <t>649365</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>751485</t>
+          <t>746307</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>347008</t>
+          <t>349214</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>423988</t>
+          <t>425286</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1022256</t>
+          <t>1028186</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1145820</t>
+          <t>1150248</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>75722</t>
+          <t>73346</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>113526</t>
+          <t>113994</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>58645</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>95213</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>141747</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>194822</t>
+          <t>194392</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1040666</t>
+          <t>1036826</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1149785</t>
+          <t>1152793</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>802031</t>
+          <t>796534</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>906344</t>
+          <t>899568</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1866642</t>
+          <t>1866941</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2018816</t>
+          <t>2019238</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">

--- a/data/trans_orig/P23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200966</t>
+          <t>200725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>246032</t>
+          <t>246811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159092</t>
+          <t>158423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194484</t>
+          <t>193015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>372438</t>
+          <t>372050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>429929</t>
+          <t>429095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81590</t>
+          <t>80632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117623</t>
+          <t>115475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>27853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115709</t>
+          <t>116653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158370</t>
+          <t>157492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23326</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>34533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119801</t>
+          <t>119902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157760</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>67256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98554</t>
+          <t>97110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195609</t>
+          <t>194538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245757</t>
+          <t>246142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131667</t>
+          <t>132371</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170129</t>
+          <t>169853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177290</t>
+          <t>178821</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215606</t>
+          <t>217349</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>321913</t>
+          <t>320683</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>377470</t>
+          <t>375808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65035</t>
+          <t>64658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96865</t>
+          <t>97146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54835</t>
+          <t>54452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143793</t>
+          <t>142707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>25143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>108964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>145387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>98815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137325</t>
+          <t>135228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216431</t>
+          <t>219311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>271096</t>
+          <t>270345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158330</t>
+          <t>159557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204783</t>
+          <t>204368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>85714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109766</t>
+          <t>109748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>249994</t>
+          <t>252519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301296</t>
+          <t>303378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>87849</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>127016</t>
+          <t>126938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33993</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>112471</t>
+          <t>110318</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154047</t>
+          <t>151159</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219637</t>
+          <t>221097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263805</t>
+          <t>267629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54145</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260926</t>
+          <t>259044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>311245</t>
+          <t>312038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>366817</t>
+          <t>369672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>434101</t>
+          <t>434722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>383331</t>
+          <t>381689</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>435211</t>
+          <t>432541</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>766692</t>
+          <t>768894</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>854846</t>
+          <t>858942</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244651</t>
+          <t>242893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301863</t>
+          <t>305356</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50362</t>
+          <t>50195</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81573</t>
+          <t>82456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>306008</t>
+          <t>307150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>371766</t>
+          <t>371351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41661</t>
+          <t>41332</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64197</t>
+          <t>64724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>500530</t>
+          <t>499123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>569820</t>
+          <t>568735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198059</t>
+          <t>200967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247323</t>
+          <t>249357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>711167</t>
+          <t>711391</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>799186</t>
+          <t>798286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82448</t>
+          <t>80955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116504</t>
+          <t>115380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>323938</t>
+          <t>324963</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>372970</t>
+          <t>371756</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>412694</t>
+          <t>415903</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>479897</t>
+          <t>478331</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80810</t>
+          <t>79631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>51963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86961</t>
+          <t>87149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125162</t>
+          <t>124897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>163805</t>
+          <t>164294</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>201332</t>
+          <t>201055</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>144133</t>
+          <t>144605</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>188354</t>
+          <t>188866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>315824</t>
+          <t>315876</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>380427</t>
+          <t>376493</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>188605</t>
+          <t>188676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>219076</t>
+          <t>219355</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1001316</t>
+          <t>1005442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1055397</t>
+          <t>1056143</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1200075</t>
+          <t>1202649</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1262254</t>
+          <t>1263908</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36266</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62776</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41844</t>
+          <t>40363</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>69973</t>
+          <t>69737</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29560</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49598</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87063</t>
+          <t>85860</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>129832</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>173888</t>
+          <t>172603</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>196717</t>
+          <t>193814</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>250214</t>
+          <t>250489</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1202151</t>
+          <t>1202924</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1310592</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2203643</t>
+          <t>2207895</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2313629</t>
+          <t>2313856</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3432978</t>
+          <t>3446835</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3602558</t>
+          <t>3603846</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>582596</t>
+          <t>584288</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>674154</t>
+          <t>675560</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>227695</t>
+          <t>228401</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>288229</t>
+          <t>288018</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>833659</t>
+          <t>828094</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>951343</t>
+          <t>937205</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>67903</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>103795</t>
+          <t>104036</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68099</t>
+          <t>68393</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>105600</t>
+          <t>104302</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>145386</t>
+          <t>147077</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>196421</t>
+          <t>195510</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1240952</t>
+          <t>1246005</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1354630</t>
+          <t>1355224</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>726506</t>
+          <t>727020</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>821358</t>
+          <t>825965</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2002032</t>
+          <t>1999058</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2155898</t>
+          <t>2142092</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154923</t>
+          <t>155568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198086</t>
+          <t>198361</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143378</t>
+          <t>143484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179108</t>
+          <t>180614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>311951</t>
+          <t>311327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>369585</t>
+          <t>367802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94352</t>
+          <t>94347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133980</t>
+          <t>132705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39702</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>67844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142476</t>
+          <t>140498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191180</t>
+          <t>191452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119809</t>
+          <t>119581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162288</t>
+          <t>161417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72818</t>
+          <t>72824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107333</t>
+          <t>108066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>205099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256633</t>
+          <t>258227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154237</t>
+          <t>154289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198214</t>
+          <t>198234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138637</t>
+          <t>139187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177145</t>
+          <t>179094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>306211</t>
+          <t>302698</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>363155</t>
+          <t>365814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75480</t>
+          <t>77102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111744</t>
+          <t>113870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>40664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>68817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124186</t>
+          <t>125774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170893</t>
+          <t>173551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119145</t>
+          <t>116690</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158126</t>
+          <t>159143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97057</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133164</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>226664</t>
+          <t>223393</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>281821</t>
+          <t>279372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163303</t>
+          <t>163876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213953</t>
+          <t>212440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123827</t>
+          <t>123423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156221</t>
+          <t>154820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297106</t>
+          <t>301420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357282</t>
+          <t>360800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145782</t>
+          <t>145865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190495</t>
+          <t>190182</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176222</t>
+          <t>178136</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>234704</t>
+          <t>229479</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233727</t>
+          <t>231845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285974</t>
+          <t>283767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>64375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93297</t>
+          <t>93859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306356</t>
+          <t>306042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366979</t>
+          <t>361435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>297133</t>
+          <t>295605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>360230</t>
+          <t>360029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>336778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394972</t>
+          <t>392426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>650203</t>
+          <t>652314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>738340</t>
+          <t>741624</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300537</t>
+          <t>298352</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361610</t>
+          <t>361513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94956</t>
+          <t>94821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135730</t>
+          <t>137674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>405378</t>
+          <t>404650</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481597</t>
+          <t>480587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>41156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61452</t>
+          <t>60292</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>435598</t>
+          <t>439233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>506014</t>
+          <t>506681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>240548</t>
+          <t>240144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294667</t>
+          <t>296322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>696654</t>
+          <t>690505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>785755</t>
+          <t>784892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>138097</t>
+          <t>139804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>182909</t>
+          <t>182139</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>446606</t>
+          <t>445180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>498777</t>
+          <t>500581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>600590</t>
+          <t>597401</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>672559</t>
+          <t>668947</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111400</t>
+          <t>111653</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>151801</t>
+          <t>151271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>56014</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91686</t>
+          <t>89680</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174906</t>
+          <t>176907</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228818</t>
+          <t>230712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25066</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,47 +7501,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>20238</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>3,3%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>18888</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>41402</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>180572</t>
+          <t>182569</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>225996</t>
+          <t>226126</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>177357</t>
+          <t>175310</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>226910</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>371815</t>
+          <t>371346</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>441295</t>
+          <t>440043</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>180261</t>
+          <t>181682</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>210709</t>
+          <t>210798</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>853332</t>
+          <t>854657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>908466</t>
+          <t>912401</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1049192</t>
+          <t>1048787</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1110949</t>
+          <t>1107418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7907,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48373</t>
+          <t>49181</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81184</t>
+          <t>79765</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>88745</t>
+          <t>86208</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>43052</t>
+          <t>41901</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>58816</t>
+          <t>59535</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>129983</t>
+          <t>127994</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>175235</t>
+          <t>173888</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>173191</t>
+          <t>170341</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>224720</t>
+          <t>223831</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1171255</t>
+          <t>1174197</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1290709</t>
+          <t>1288803</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2124880</t>
+          <t>2119124</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2242604</t>
+          <t>2239572</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3323450</t>
+          <t>3321326</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3491352</t>
+          <t>3498063</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>786718</t>
+          <t>785918</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>886402</t>
+          <t>891548</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>350579</t>
+          <t>354613</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>431751</t>
+          <t>431340</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1166612</t>
+          <t>1160397</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1299018</t>
+          <t>1295487</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77531</t>
+          <t>76693</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>120744</t>
+          <t>119019</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>55682</t>
+          <t>57034</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>92459</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>145122</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>198099</t>
+          <t>200086</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1195626</t>
+          <t>1201547</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1314748</t>
+          <t>1318648</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>843704</t>
+          <t>848767</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>954558</t>
+          <t>955493</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2087589</t>
+          <t>2081712</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2252006</t>
+          <t>2246575</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197925</t>
+          <t>197202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240560</t>
+          <t>239361</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192110</t>
+          <t>192023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230363</t>
+          <t>230344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>399685</t>
+          <t>404543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>457864</t>
+          <t>461642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84145</t>
+          <t>84646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119874</t>
+          <t>123269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54118</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>85451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148848</t>
+          <t>145614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193234</t>
+          <t>194829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75427</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>74168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129126</t>
+          <t>130099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175598</t>
+          <t>175837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166641</t>
+          <t>167425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>206165</t>
+          <t>205073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181999</t>
+          <t>181101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220586</t>
+          <t>219346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>360795</t>
+          <t>356979</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>417539</t>
+          <t>414703</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68551</t>
+          <t>67855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100897</t>
+          <t>102002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131516</t>
+          <t>132757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>176432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>30997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78210</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112192</t>
+          <t>114440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75456</t>
+          <t>76777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111041</t>
+          <t>109448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>164405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>211302</t>
+          <t>213254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165967</t>
+          <t>166005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210640</t>
+          <t>210804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83877</t>
+          <t>83958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109568</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260234</t>
+          <t>257781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312401</t>
+          <t>311050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99205</t>
+          <t>98446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>137937</t>
+          <t>140139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114496</t>
+          <t>114280</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>157274</t>
+          <t>155996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>32153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179793</t>
+          <t>180886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225020</t>
+          <t>228338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35042</t>
+          <t>35246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59459</t>
+          <t>58973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224165</t>
+          <t>222781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276612</t>
+          <t>275980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>414289</t>
+          <t>417005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>482575</t>
+          <t>484617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>378473</t>
+          <t>379913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>438656</t>
+          <t>436386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>813961</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>905908</t>
+          <t>899549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232900</t>
+          <t>232245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290960</t>
+          <t>292044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>80907</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122678</t>
+          <t>119332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>325949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394548</t>
+          <t>398165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45202</t>
+          <t>44173</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>47718</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80892</t>
+          <t>79603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>371853</t>
+          <t>372623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>441491</t>
+          <t>438293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259096</t>
+          <t>256277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313286</t>
+          <t>313277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>644590</t>
+          <t>650045</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>729266</t>
+          <t>732453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>225228</t>
+          <t>227028</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275194</t>
+          <t>275528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>409795</t>
+          <t>410685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>465477</t>
+          <t>460739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>651861</t>
+          <t>649478</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>727648</t>
+          <t>725574</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>108456</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149645</t>
+          <t>148701</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101886</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185429</t>
+          <t>185629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240435</t>
+          <t>239334</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,82 +11683,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3068</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>15176</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>17712</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>10809</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>27825</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>7989</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>14789</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>17712</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>11507</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>28067</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>207395</t>
+          <t>209810</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>258786</t>
+          <t>256512</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>184909</t>
+          <t>186563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>235477</t>
+          <t>235791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>407935</t>
+          <t>408325</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>476963</t>
+          <t>476171</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>190827</t>
+          <t>192281</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>222232</t>
+          <t>224109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>827937</t>
+          <t>833199</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>885983</t>
+          <t>884406</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1036297</t>
+          <t>1037945</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1097698</t>
+          <t>1098558</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>40395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68023</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>34131</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>49571</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79839</t>
+          <t>77888</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135873</t>
+          <t>138075</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>187271</t>
+          <t>183421</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>197126</t>
+          <t>196647</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>253547</t>
+          <t>251613</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1435251</t>
+          <t>1447030</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1553266</t>
+          <t>1559725</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2158313</t>
+          <t>2157488</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2274102</t>
+          <t>2273796</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3629976</t>
+          <t>3626895</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3807182</t>
+          <t>3795851</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>649365</t>
+          <t>655234</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>746307</t>
+          <t>751958</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>349214</t>
+          <t>352023</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>425286</t>
+          <t>428245</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1028186</t>
+          <t>1019582</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1150248</t>
+          <t>1138610</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>73346</t>
+          <t>74672</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>113994</t>
+          <t>114132</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>58715</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>95213</t>
+          <t>93904</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>141747</t>
+          <t>142683</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>194392</t>
+          <t>195070</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1036826</t>
+          <t>1037514</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1152793</t>
+          <t>1147025</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>796534</t>
+          <t>800532</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>899568</t>
+          <t>900913</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1866941</t>
+          <t>1866450</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2019238</t>
+          <t>2018267</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
